--- a/data/trans_orig/IQ3006_MoAR-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ3006_MoAR-Clase-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la edad en años en la que empezaron a beber leche normal</t>
+          <t>Menores según la edad en años en la que empezaron a beber leche normal (tasa de respuesta: 32,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,59; 16,58</t>
+          <t>9,08; 16,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,52; 14,55</t>
+          <t>10,64; 14,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,72; 14,81</t>
+          <t>8,74; 15,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,44; 14,35</t>
+          <t>9,79; 14,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,56; 18,4</t>
+          <t>11,12; 18,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,57; 19,3</t>
+          <t>10,68; 18,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,64; 14,69</t>
+          <t>10,6; 14,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,75; 15,97</t>
+          <t>11,96; 15,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,56; 16,04</t>
+          <t>10,59; 16,09</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,01; 16,6</t>
+          <t>10,01; 16,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,61; 14,5</t>
+          <t>11,54; 14,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,9; 19,39</t>
+          <t>12,11; 19,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,59; 13,45</t>
+          <t>8,43; 13,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,0; 14,01</t>
+          <t>12,0; 13,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,69; 16,77</t>
+          <t>10,67; 17,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,54; 13,38</t>
+          <t>9,32; 13,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,93; 14,09</t>
+          <t>11,9; 13,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,09; 16,72</t>
+          <t>11,88; 16,48</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,78; 16,96</t>
+          <t>9,1; 16,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,33; 16,35</t>
+          <t>11,27; 16,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -912,32 +912,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,99; 17,97</t>
+          <t>10,99; 18,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,11; 16,84</t>
+          <t>9,1; 17,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,0; 21,69</t>
+          <t>12,0; 21,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,34; 16,02</t>
+          <t>11,29; 16,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,9; 15,58</t>
+          <t>10,91; 15,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,0; 18,38</t>
+          <t>12,0; 19,19</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,15; 16,38</t>
+          <t>10,0; 16,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,59; 16,8</t>
+          <t>12,41; 16,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,59; 15,49</t>
+          <t>11,41; 15,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,53; 14,01</t>
+          <t>11,47; 13,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,94; 15,72</t>
+          <t>11,31; 16,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,29; 14,61</t>
+          <t>10,4; 14,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,32; 14,58</t>
+          <t>11,2; 14,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,48; 15,53</t>
+          <t>12,53; 15,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,33; 14,19</t>
+          <t>11,56; 14,53</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,69; 17,25</t>
+          <t>11,76; 17,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,52; 15,19</t>
+          <t>10,96; 15,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,69; 12,0</t>
+          <t>10,7; 12,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,7; 14,2</t>
+          <t>8,51; 13,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,64; 13,91</t>
+          <t>9,14; 13,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,3; 10,83</t>
+          <t>6,49; 10,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,56; 14,41</t>
+          <t>10,29; 14,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,61; 14,03</t>
+          <t>10,6; 13,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,91; 11,2</t>
+          <t>7,99; 11,15</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,0; 16,0</t>
+          <t>9,06; 16,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,0; 22,42</t>
+          <t>12,0; 22,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,19; 21,13</t>
+          <t>10,29; 21,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,57; 18,39</t>
+          <t>11,45; 18,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,0; 18,39</t>
+          <t>12,0; 18,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,7; 12,41</t>
+          <t>10,11; 12,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,75; 17,28</t>
+          <t>11,78; 17,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,32; 20,29</t>
+          <t>13,29; 20,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,16; 17,92</t>
+          <t>10,91; 17,84</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,96; 14,97</t>
+          <t>11,8; 14,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,83; 14,76</t>
+          <t>12,66; 14,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,69; 14,33</t>
+          <t>11,92; 14,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,49; 13,52</t>
+          <t>11,47; 13,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,13; 14,6</t>
+          <t>12,03; 14,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,19; 13,96</t>
+          <t>11,26; 14,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,94; 13,72</t>
+          <t>12,03; 13,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,77; 14,39</t>
+          <t>12,76; 14,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,88; 13,77</t>
+          <t>11,92; 13,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3006_MoAR-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ3006_MoAR-Clase-trans_orig.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,08; 16,46</t>
+          <t>9,54; 16,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,64; 14,36</t>
+          <t>10,6; 14,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,74; 15,05</t>
+          <t>8,58; 15,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,79; 14,43</t>
+          <t>9,36; 14,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,12; 18,06</t>
+          <t>11,12; 17,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,68; 18,91</t>
+          <t>10,34; 18,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,6; 14,83</t>
+          <t>10,57; 14,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,96; 15,99</t>
+          <t>11,74; 15,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,59; 16,09</t>
+          <t>10,52; 16,39</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,01; 16,54</t>
+          <t>10,01; 16,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,54; 14,49</t>
+          <t>11,63; 14,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,11; 19,21</t>
+          <t>11,89; 19,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,43; 13,47</t>
+          <t>8,55; 13,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,0; 13,98</t>
+          <t>12,0; 14,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,67; 17,44</t>
+          <t>10,64; 17,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,32; 13,6</t>
+          <t>9,5; 13,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,9; 13,98</t>
+          <t>11,92; 13,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,88; 16,48</t>
+          <t>11,73; 16,81</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,1; 16,96</t>
+          <t>10,0; 16,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,27; 16,23</t>
+          <t>11,28; 16,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -912,32 +912,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,99; 18,01</t>
+          <t>11,0; 17,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,1; 17,1</t>
+          <t>9,68; 16,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,0; 21,47</t>
+          <t>12,0; 21,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,29; 16,0</t>
+          <t>10,95; 15,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,91; 15,58</t>
+          <t>11,05; 15,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,0; 19,19</t>
+          <t>12,0; 19,64</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,0; 16,02</t>
+          <t>10,37; 16,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,41; 16,69</t>
+          <t>12,48; 16,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,41; 15,44</t>
+          <t>11,51; 15,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,47; 13,92</t>
+          <t>11,42; 13,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,31; 16,06</t>
+          <t>11,18; 15,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,4; 14,79</t>
+          <t>10,37; 14,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,2; 14,6</t>
+          <t>11,37; 14,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,53; 15,51</t>
+          <t>12,39; 15,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,56; 14,53</t>
+          <t>11,38; 14,27</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,76; 17,15</t>
+          <t>11,61; 16,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,96; 15,63</t>
+          <t>10,74; 15,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1132,32 +1132,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,51; 13,85</t>
+          <t>8,99; 13,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,14; 13,97</t>
+          <t>8,39; 13,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,49; 10,85</t>
+          <t>6,49; 10,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,29; 14,16</t>
+          <t>10,26; 14,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,6; 13,9</t>
+          <t>10,59; 14,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,99; 11,15</t>
+          <t>8,13; 11,2</t>
         </is>
       </c>
     </row>
@@ -1227,27 +1227,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,06; 16,0</t>
+          <t>9,0; 16,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,0; 22,51</t>
+          <t>12,0; 22,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,29; 21,16</t>
+          <t>10,18; 21,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,45; 18,32</t>
+          <t>11,77; 18,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,0; 18,49</t>
+          <t>12,0; 18,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,78; 17,31</t>
+          <t>11,87; 17,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,29; 20,41</t>
+          <t>13,32; 20,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,91; 17,84</t>
+          <t>11,09; 18,13</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,8; 14,69</t>
+          <t>11,74; 14,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,66; 14,74</t>
+          <t>12,72; 14,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,92; 14,41</t>
+          <t>11,92; 14,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,47; 13,52</t>
+          <t>11,5; 13,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,03; 14,51</t>
+          <t>12,15; 14,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,26; 14,07</t>
+          <t>11,18; 13,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,03; 13,72</t>
+          <t>11,92; 13,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,76; 14,35</t>
+          <t>12,74; 14,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,92; 13,82</t>
+          <t>11,88; 13,76</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3006_MoAR-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ3006_MoAR-Clase-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12,36</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14,72</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14,82</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>13,26</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>12,72</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11,01</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12,36</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>14,72</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,82</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,54; 16,85</t>
+          <t>9,44; 14,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,6; 14,33</t>
+          <t>11,56; 18,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,58; 15,0</t>
+          <t>10,57; 19,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,36; 14,41</t>
+          <t>9,59; 16,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,12; 17,97</t>
+          <t>10,52; 14,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,34; 18,87</t>
+          <t>8,72; 14,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,57; 14,73</t>
+          <t>10,64; 14,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,74; 15,65</t>
+          <t>11,75; 15,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,52; 16,39</t>
+          <t>10,56; 16,04</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>11,46</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12,8</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13,13</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>12,63</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>12,96</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>14,93</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11,46</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>12,8</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>13,13</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8,59; 13,45</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12,0; 14,01</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10,69; 16,77</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>10,01; 16,6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>11,63; 14,51</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11,89; 19,6</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8,55; 13,59</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,0; 14,09</t>
+          <t>11,61; 14,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,64; 17,06</t>
+          <t>11,9; 19,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,5; 13,69</t>
+          <t>9,54; 13,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,92; 13,95</t>
+          <t>11,93; 14,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,73; 16,81</t>
+          <t>12,09; 16,72</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>12,96</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>13,46</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14,48</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>13,96</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>13,38</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>12,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12,96</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13,46</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14,48</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,0; 16,96</t>
+          <t>10,99; 17,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,28; 16,2</t>
+          <t>9,11; 16,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>12,0; 21,69</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>9,78; 16,96</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>11,33; 16,35</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>11,0; 17,96</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>9,68; 16,65</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>12,0; 21,39</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,95; 15,78</t>
+          <t>11,34; 16,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,05; 15,8</t>
+          <t>10,9; 15,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,0; 19,64</t>
+          <t>12,0; 18,38</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12,58</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13,59</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12,17</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>13,4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>14,33</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>13,37</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12,58</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,59</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,17</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,37; 16,24</t>
+          <t>11,53; 14,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,48; 16,63</t>
+          <t>10,94; 15,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,51; 15,34</t>
+          <t>10,29; 14,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,42; 13,94</t>
+          <t>10,15; 16,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,18; 15,92</t>
+          <t>12,59; 16,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,37; 14,75</t>
+          <t>11,59; 15,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,37; 14,59</t>
+          <t>11,32; 14,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,39; 15,28</t>
+          <t>12,48; 15,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,38; 14,27</t>
+          <t>11,33; 14,19</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11,33</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11,82</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>8,73</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>13,6</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>12,78</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>11,51</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>11,33</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>11,82</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>8,73</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,61; 16,77</t>
+          <t>8,7; 14,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,74; 15,59</t>
+          <t>8,64; 13,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,7; 12,0</t>
+          <t>6,3; 10,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,99; 13,91</t>
+          <t>11,69; 17,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,39; 13,88</t>
+          <t>10,52; 15,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,49; 10,84</t>
+          <t>10,69; 12,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,26; 14,2</t>
+          <t>10,56; 14,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,59; 14,1</t>
+          <t>10,61; 14,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,13; 11,2</t>
+          <t>7,91; 11,2</t>
         </is>
       </c>
     </row>
@@ -1174,32 +1174,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>14,95</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15,02</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11,57</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>12,3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>16,6</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>15,17</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>14,95</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>15,02</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>11,57</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>11,57; 18,39</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>12,0; 18,39</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>9,7; 12,41</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>9,0; 16,0</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>12,0; 22,57</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>10,18; 21,14</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>11,77; 18,27</t>
-        </is>
-      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,0; 18,72</t>
+          <t>12,0; 22,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,11; 12,41</t>
+          <t>10,19; 21,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,87; 17,36</t>
+          <t>11,75; 17,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,32; 20,16</t>
+          <t>13,32; 20,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,09; 18,13</t>
+          <t>11,16; 17,92</t>
         </is>
       </c>
     </row>
@@ -1284,32 +1284,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>12,46</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13,42</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12,52</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>13,39</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>13,67</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>13,1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>12,46</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>13,42</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>12,52</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,74; 14,85</t>
+          <t>11,49; 13,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,72; 14,81</t>
+          <t>12,13; 14,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,92; 14,53</t>
+          <t>11,19; 13,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,5; 13,53</t>
+          <t>11,96; 14,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,15; 14,61</t>
+          <t>12,83; 14,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,18; 13,83</t>
+          <t>11,69; 14,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,92; 13,7</t>
+          <t>11,94; 13,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,74; 14,38</t>
+          <t>12,77; 14,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,88; 13,76</t>
+          <t>11,88; 13,77</t>
         </is>
       </c>
     </row>
